--- a/referral_form_templates/019_dj_service_referral_form--referral_form_templates.xlsx
+++ b/referral_form_templates/019_dj_service_referral_form--referral_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'new_client',_'label':_'new_client'}</t>
+          <t>new_client</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'New Client', 'label': 'New Client'}</t>
+          <t>New Client</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'returning_client',_'label':_'returning_client'}</t>
+          <t>returning_client</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Returning Client', 'label': 'Returning Client'}</t>
+          <t>Returning Client</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'wedding',_'label':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Wedding', 'label': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'corporate_event',_'label':_'corporate_event'}</t>
+          <t>corporate_event</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Corporate Event', 'label': 'Corporate Event'}</t>
+          <t>Corporate Event</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'private_party',_'label':_'private_party'}</t>
+          <t>private_party</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Private Party', 'label': 'Private Party'}</t>
+          <t>Private Party</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'bar/bat_mitzvah',_'label':_'bar/bat_mitzvah'}</t>
+          <t>bar/bat_mitzvah</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Bar/Bat Mitzvah', 'label': 'Bar/Bat Mitzvah'}</t>
+          <t>Bar/Bat Mitzvah</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'club_night',_'label':_'club_night'}</t>
+          <t>club_night</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Club Night', 'label': 'Club Night'}</t>
+          <t>Club Night</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
